--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907927F3-58B9-40A1-9AA6-19E4124B8208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45DEECA-E6F0-4A14-80D1-3E027AB690E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3590" yWindow="2010" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -107,6 +107,9 @@
     <t>帮助界面</t>
   </si>
   <si>
+    <t>GenAtom/UIHelp</t>
+  </si>
+  <si>
     <t>Pop</t>
   </si>
   <si>
@@ -116,12 +119,18 @@
     <t>大厅面</t>
   </si>
   <si>
+    <t>GenAtom/UILobby</t>
+  </si>
+  <si>
     <t>UILogin</t>
   </si>
   <si>
     <t>登录界面</t>
   </si>
   <si>
+    <t>GenAtom/UILogin</t>
+  </si>
+  <si>
     <t>Default</t>
   </si>
   <si>
@@ -182,16 +191,13 @@
     <t>Hot/AboutForm</t>
   </si>
   <si>
-    <t>GenAtom/UIHelp</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GenAtom/UILobby</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GenAtom/UILogin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>UISkill</t>
+  </si>
+  <si>
+    <t>技能界面</t>
+  </si>
+  <si>
+    <t>GenAtom/UISkill</t>
   </si>
 </sst>
 </file>
@@ -207,14 +213,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -246,7 +253,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,10 +560,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.90625" style="1"/>
+    <col min="1" max="1" width="8.90625" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="20.7265625" style="1" customWidth="1"/>
     <col min="4" max="4" width="22" style="1" customWidth="1"/>
@@ -564,7 +571,8 @@
     <col min="6" max="6" width="14.6328125" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.08984375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.90625" style="1"/>
+    <col min="9" max="9" width="8.90625" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -656,10 +664,10 @@
         <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="1" t="b">
         <v>0</v>
@@ -673,16 +681,16 @@
         <v>802</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="G5" s="1" t="b">
         <v>0</v>
@@ -696,16 +704,16 @@
         <v>803</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G6" s="1" t="b">
         <v>0</v>
@@ -719,16 +727,16 @@
         <v>901</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G7" s="1" t="b">
         <v>0</v>
@@ -742,16 +750,16 @@
         <v>902</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1" t="b">
         <v>0</v>
@@ -765,16 +773,16 @@
         <v>903</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="b">
         <v>0</v>
@@ -788,16 +796,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1" t="b">
         <v>1</v>
@@ -811,16 +819,16 @@
         <v>100</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="b">
         <v>0</v>
@@ -834,16 +842,16 @@
         <v>101</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12" s="1" t="b">
         <v>0</v>
@@ -857,16 +865,16 @@
         <v>102</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G13" s="1" t="b">
         <v>0</v>
@@ -875,8 +883,33 @@
         <v>1</v>
       </c>
     </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>804</v>
+      </c>
+      <c r="C14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="b">
+        <f>FALSE</f>
+        <v>0</v>
+      </c>
+      <c r="H14" t="b">
+        <f>FALSE</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778E5174-2065-4B5D-98F2-1B20BA92C89B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB51B3F4-B9C6-4846-8979-8239817FDA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -214,6 +214,14 @@
   </si>
   <si>
     <t>GenAtom/UIMain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIFormFight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom/UIFormFight</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -578,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1" customWidth="1"/>
@@ -965,6 +973,29 @@
       <c r="G16" t="b">
         <v>0</v>
       </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>807</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB51B3F4-B9C6-4846-8979-8239817FDA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E389CF-0212-4C5E-8A1A-414E34BF21B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5080" yWindow="3070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
   <si>
     <t>##var</t>
   </si>
@@ -222,6 +222,14 @@
   </si>
   <si>
     <t>GenAtom/UIFormFight</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIFormMap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom/UIFormMap</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -586,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1" customWidth="1"/>
@@ -997,6 +1005,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>808</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E389CF-0212-4C5E-8A1A-414E34BF21B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5465F2-6F37-4776-BC19-402B7281B4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="3070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -230,6 +230,14 @@
   </si>
   <si>
     <t>GenAtom/UIFormMap</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIFormBag1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom/UIFormBag1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1" customWidth="1"/>
@@ -1021,6 +1029,29 @@
       <c r="G18" t="b">
         <v>0</v>
       </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="1">
+        <v>809</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5465F2-6F37-4776-BC19-402B7281B4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578A415-C688-4229-8BE7-7582AEA04B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
@@ -238,6 +238,14 @@
   </si>
   <si>
     <t>GenAtom/UIFormBag1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIFormSkills</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom/UIFormSkills</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1" customWidth="1"/>
@@ -1053,6 +1061,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="1">
+        <v>810</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Design/Excel/ET/Datas/Game/UI.xlsx
+++ b/Design/Excel/ET/Datas/Game/UI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A578A415-C688-4229-8BE7-7582AEA04B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B37F82-5ECA-436A-B61E-3399A6F6684A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2210" yWindow="2070" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UI界面" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="70">
   <si>
     <t>##var</t>
   </si>
@@ -246,6 +246,14 @@
   </si>
   <si>
     <t>GenAtom/UIFormSkills</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIFormShop</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GenAtom/UIFormShop</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -610,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1" customWidth="1"/>
@@ -1081,6 +1089,26 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="1">
+        <v>811</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
